--- a/data/recruiterList.xlsx
+++ b/data/recruiterList.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sameer\Desktop\Linkedin Automation Testing Project\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sameer\Desktop\Linkedin-Automation-Testing-Project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B296974-2BD0-4012-951B-27B0A2106792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73AAEB26-E6C1-45C2-9211-CEFC9A9C9254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>First Name</t>
   </si>
@@ -33,16 +33,7 @@
     <t>Last Name</t>
   </si>
   <si>
-    <t>Rony</t>
-  </si>
-  <si>
     <t>jh</t>
-  </si>
-  <si>
-    <t>sameer</t>
-  </si>
-  <si>
-    <t>studyprep</t>
   </si>
 </sst>
 </file>
@@ -379,18 +370,10 @@
       </c>
     </row>
     <row r="2" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
+      <c r="B2" s="1"/>
     </row>
     <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
         <v>2</v>
       </c>
     </row>
